--- a/public/sap-reporting/expansion-150-downloads/EXT-PP13-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP13-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rf2100c89c7904ae3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R008f97b4dd8d477f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rbe7f53296a6a4755"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rc4999cc581d84141"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rb1c947be31cc4616"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R9070bf65df714db9"/>
   </x:sheets>
 </x:workbook>
 </file>
